--- a/artfynd/A 495-2020 artfynd.xlsx
+++ b/artfynd/A 495-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 495-2020 artfynd.xlsx
+++ b/artfynd/A 495-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>126865268</v>
       </c>
       <c r="B3" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>126865262</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>126865264</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>126868615</v>
       </c>
       <c r="B6" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>126861200</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1358,7 +1358,7 @@
         <v>126861154</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>126861181</v>
       </c>
       <c r="B9" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>126861146</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>126865318</v>
       </c>
       <c r="B11" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,45 +1759,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126865263</v>
+        <v>126861361</v>
       </c>
       <c r="B12" t="n">
-        <v>80018</v>
+        <v>78678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6457</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>678040</v>
+        <v>677908</v>
       </c>
       <c r="R12" t="n">
-        <v>7105617</v>
+        <v>7105727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,30 +1841,15 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1875,45 +1860,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126861361</v>
+        <v>126865263</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>80049</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6457</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677908</v>
+        <v>678040</v>
       </c>
       <c r="R13" t="n">
-        <v>7105727</v>
+        <v>7105617</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,15 +1942,30 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1979,7 +1979,7 @@
         <v>126861372</v>
       </c>
       <c r="B14" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>126865265</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>126865232</v>
       </c>
       <c r="B16" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>126865266</v>
       </c>
       <c r="B17" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126865267</v>
+        <v>126861360</v>
       </c>
       <c r="B19" t="n">
-        <v>75070</v>
+        <v>78678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,34 +2535,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>678035</v>
+        <v>677895</v>
       </c>
       <c r="R19" t="n">
-        <v>7105625</v>
+        <v>7105725</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,30 +2606,15 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2640,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126861360</v>
+        <v>126865267</v>
       </c>
       <c r="B20" t="n">
-        <v>78647</v>
+        <v>75130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2651,34 +2636,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>677895</v>
+        <v>678035</v>
       </c>
       <c r="R20" t="n">
-        <v>7105725</v>
+        <v>7105625</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2722,15 +2707,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2744,7 +2744,7 @@
         <v>126865303</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>126861369</v>
       </c>
       <c r="B22" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126865270</v>
+        <v>126868562</v>
       </c>
       <c r="B23" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,14 +2974,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råtjärnberget, Ång</t>
+          <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>678055</v>
+        <v>678071</v>
       </c>
       <c r="R23" t="n">
-        <v>7105689</v>
+        <v>7105674</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3025,30 +3025,15 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
+          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3059,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126868562</v>
+        <v>126865270</v>
       </c>
       <c r="B24" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,14 +3075,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Råtjärnsberget, Ång</t>
+          <t>Råtjärnberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>678071</v>
+        <v>678055</v>
       </c>
       <c r="R24" t="n">
-        <v>7105674</v>
+        <v>7105689</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,15 +3126,30 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Malin Löfgren, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Martin Axegård</t>
+          <t>Peder Winding, Malin Löfgren, Philipp Weiss, Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3160,32 +3160,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126861086</v>
+        <v>126861130</v>
       </c>
       <c r="B25" t="n">
-        <v>80112</v>
+        <v>78770</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>677857</v>
+        <v>677908</v>
       </c>
       <c r="R25" t="n">
-        <v>7105746</v>
+        <v>7105725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3261,45 +3261,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126861130</v>
+        <v>126861345</v>
       </c>
       <c r="B26" t="n">
-        <v>78739</v>
+        <v>91893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>677908</v>
+        <v>677882</v>
       </c>
       <c r="R26" t="n">
-        <v>7105725</v>
+        <v>7105774</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,6 +3349,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3362,54 +3372,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126861345</v>
+        <v>126861086</v>
       </c>
       <c r="B27" t="n">
-        <v>91819</v>
+        <v>80143</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Råtjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677882</v>
+        <v>677857</v>
       </c>
       <c r="R27" t="n">
-        <v>7105774</v>
+        <v>7105746</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3450,7 +3451,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3473,10 +3473,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126861234</v>
+        <v>126861183</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,21 +3484,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>677892</v>
+        <v>677887</v>
       </c>
       <c r="R28" t="n">
-        <v>7105769</v>
+        <v>7105763</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126861183</v>
+        <v>126861234</v>
       </c>
       <c r="B29" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,21 +3585,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677887</v>
+        <v>677892</v>
       </c>
       <c r="R29" t="n">
-        <v>7105763</v>
+        <v>7105769</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
         <v>126861232</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>126861040</v>
       </c>
       <c r="B31" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>126865290</v>
       </c>
       <c r="B32" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Carl Jansson, Cajsa Björkén, Fredrik Wilde, Peder Winding, Malin Löfgren, Mattias Dalkvist, Hedda Bring, Vilhelm Kroon, Martin Axegård</t>
+          <t>Martin Axegård, Vilhelm Kroon, Hedda Bring, Mattias Dalkvist, Malin Löfgren, Peder Winding, Fredrik Wilde, Cajsa Björkén, Carl Jansson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4082,7 +4082,7 @@
         <v>126861042</v>
       </c>
       <c r="B34" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>126865249</v>
       </c>
       <c r="B35" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>126861131</v>
       </c>
       <c r="B36" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
